--- a/docs/downloads/经营分_鲁东省区__沂枣片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__沂枣片区_2026-10-18.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -946,34 +946,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>临沂市</t>
+          <t>枣庄市</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7354607399531743295</t>
+          <t>6864139944475035656</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0山东省临沂市郯城郯东路店）</t>
+          <t>维也纳酒店（枣庄滕州火车站店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>维也纳酒店(临沂郯城郯东路店)</t>
+          <t>维也纳酒店(滕州火车站店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -987,13 +987,13 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>枣庄市</t>
+          <t>临沂市</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7231898729182136379</t>
+          <t>7354607399531743295</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>希岸酒店(枣庄台儿庄古城店)</t>
+          <t>维也纳酒店（5.0山东省临沂市郯城郯东路店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>希岸酒店(台儿庄古城店)</t>
+          <t>维也纳酒店(临沂郯城郯东路店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1058,14 +1058,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1075,13 +1075,13 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P6" t="n">
         <v>30</v>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7033633086059317279</t>
+          <t>7231898729182136379</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（枣庄高铁站市政府文体中心店）</t>
+          <t>希岸酒店(枣庄台儿庄古城店)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>白玉兰酒店(枣庄高铁站六盘山路店)</t>
+          <t>希岸酒店(台儿庄古城店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1163,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1175,7 +1175,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1210,22 +1210,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>临沂市</t>
+          <t>枣庄市</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7665245258367633443</t>
+          <t>7033633086059317279</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳酒店(费县蓝色港湾店)</t>
+          <t>白玉兰商务酒店（枣庄高铁站市政府文体中心店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳酒店(费县蓝色港湾店)</t>
+          <t>白玉兰酒店(枣庄高铁站六盘山路店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1237,11 +1237,11 @@
         <v>95</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1251,19 +1251,19 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>枣庄市</t>
+          <t>临沂市</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6864139944475035656</t>
+          <t>7665245258367633443</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（枣庄滕州火车站店）</t>
+          <t>维也纳酒店(费县蓝色港湾店)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳酒店(滕州火车站店)</t>
+          <t>维也纳酒店(费县蓝色港湾店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1325,11 +1325,11 @@
         <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1339,19 +1339,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="n">
         <v>25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>30</v>
-      </c>
-      <c r="O9" t="n">
-        <v>25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1853,7 +1853,7 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
